--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Healthcare ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Healthcare ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="80">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Healthcare ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,33 +70,33 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
+    <t>MAX Healthcare Institute Ltd</t>
+  </si>
+  <si>
+    <t>INE027H01010</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
     <t>Cipla Ltd.</t>
   </si>
   <si>
     <t>INE059A01026</t>
   </si>
   <si>
-    <t>MAX Healthcare Institute Ltd</t>
-  </si>
-  <si>
-    <t>INE027H01010</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
     <t>Dr. Reddy's Laboratories Ltd.</t>
   </si>
   <si>
     <t>INE089A01031</t>
   </si>
   <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
     <t>Apollo Hospitals Enterprise Ltd.</t>
   </si>
   <si>
@@ -109,16 +109,28 @@
     <t>INE326A01037</t>
   </si>
   <si>
+    <t>Fortis Healthcare Ltd.</t>
+  </si>
+  <si>
+    <t>INE061F01013</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
     <t>Aurobindo Pharma Ltd.</t>
   </si>
   <si>
     <t>INE406A01037</t>
   </si>
   <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
+    <t>Mankind Pharma Ltd</t>
+  </si>
+  <si>
+    <t>INE634S01028</t>
   </si>
   <si>
     <t>Alkem Laboratories Ltd.</t>
@@ -127,18 +139,18 @@
     <t>INE540L01014</t>
   </si>
   <si>
+    <t>Laurus Labs Ltd.</t>
+  </si>
+  <si>
+    <t>INE947Q01028</t>
+  </si>
+  <si>
     <t>Zydus Lifesciences Ltd.</t>
   </si>
   <si>
     <t>INE010B01027</t>
   </si>
   <si>
-    <t>Laurus Labs Ltd.</t>
-  </si>
-  <si>
-    <t>INE947Q01028</t>
-  </si>
-  <si>
     <t>Glenmark Pharmaceuticals Ltd.</t>
   </si>
   <si>
@@ -151,42 +163,30 @@
     <t>INE571A01038</t>
   </si>
   <si>
+    <t>Abbott India Ltd.</t>
+  </si>
+  <si>
+    <t>INE358A01014</t>
+  </si>
+  <si>
     <t>Biocon Ltd.</t>
   </si>
   <si>
     <t>INE376G01013</t>
   </si>
   <si>
-    <t>Abbott India Ltd.</t>
-  </si>
-  <si>
-    <t>INE358A01014</t>
-  </si>
-  <si>
     <t>Syngene International Ltd.</t>
   </si>
   <si>
     <t>INE398R01022</t>
   </si>
   <si>
-    <t>Dr Lal Pathlabs Ltd.</t>
-  </si>
-  <si>
-    <t>INE600L01024</t>
-  </si>
-  <si>
     <t>Granules India Ltd.</t>
   </si>
   <si>
     <t>INE101D01020</t>
   </si>
   <si>
-    <t>Metropolis Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE112L01020</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -244,7 +244,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Healthcare TRI</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J84"/>
+  <dimension ref="B1:J83"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1124,10 +1121,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>12729.939999999999</v>
+        <v>14399.779999999999</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9997084567967999</v>
+        <v>0.9999830081048001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1161,10 +1158,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>12729.939999999999</v>
+        <v>14399.779999999999</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9997084567967999</v>
+        <v>0.9999830081048001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1187,13 +1184,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>160118</v>
+        <v>168601</v>
       </c>
       <c r="G8" s="15">
-        <v>2792.38</v>
+        <v>2828.45</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2192913635565</v>
+        <v>0.1964198021967</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1216,13 +1213,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>81539</v>
+        <v>19852</v>
       </c>
       <c r="G9" s="15">
-        <v>1206.29</v>
+        <v>1312.61</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0947324429141</v>
+        <v>0.0911533159721</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1245,13 +1242,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>110082</v>
+        <v>116198</v>
       </c>
       <c r="G10" s="15">
-        <v>1168.25</v>
+        <v>1307.46</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0917450832175</v>
+        <v>0.0907956776963</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1274,13 +1271,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>90471</v>
+        <v>87954</v>
       </c>
       <c r="G11" s="15">
-        <v>1101.35</v>
+        <v>1289.14</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0864912881674</v>
+        <v>0.0895234576548</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1303,13 +1300,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>18834</v>
+        <v>95385</v>
       </c>
       <c r="G12" s="15">
-        <v>1050.50</v>
+        <v>1193.46</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0824979327369</v>
+        <v>0.0828790245999</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1332,13 +1329,13 @@
         <v>22</v>
       </c>
       <c r="F13" s="14">
-        <v>15015</v>
+        <v>15804</v>
       </c>
       <c r="G13" s="15">
-        <v>1022.60</v>
+        <v>1087.39</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0803068881645</v>
+        <v>0.075513065004</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1361,13 +1358,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>35754</v>
+        <v>37794</v>
       </c>
       <c r="G14" s="15">
-        <v>743.84</v>
+        <v>739.89</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0584152901352</v>
+        <v>0.0513811619251</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1387,16 +1384,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>41433</v>
+        <v>81470</v>
       </c>
       <c r="G15" s="15">
-        <v>485.55</v>
+        <v>575.42</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0381312434464</v>
+        <v>0.0399596537255</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1419,13 +1416,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>13926</v>
+        <v>16364</v>
       </c>
       <c r="G16" s="15">
-        <v>455.25</v>
+        <v>519.51</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0357517219214</v>
+        <v>0.036077021492</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1448,13 +1445,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>7872</v>
+        <v>43701</v>
       </c>
       <c r="G17" s="15">
-        <v>398.56</v>
+        <v>501.60</v>
       </c>
       <c r="H17" s="16">
-        <v>0.03129973924</v>
+        <v>0.034833273624</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1477,13 +1474,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>37074</v>
+        <v>17672</v>
       </c>
       <c r="G18" s="15">
-        <v>359.71</v>
+        <v>436.09</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0282487685719</v>
+        <v>0.0302839758666</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1506,13 +1503,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>58319</v>
+        <v>8328</v>
       </c>
       <c r="G19" s="15">
-        <v>340.61</v>
+        <v>424.60</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0267488061585</v>
+        <v>0.0294860605677</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1535,13 +1532,13 @@
         <v>17</v>
       </c>
       <c r="F20" s="14">
-        <v>22324</v>
+        <v>61187</v>
       </c>
       <c r="G20" s="15">
-        <v>324.41</v>
+        <v>373</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0254765867293</v>
+        <v>0.0259027333767</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1564,13 +1561,13 @@
         <v>17</v>
       </c>
       <c r="F21" s="14">
-        <v>20118</v>
+        <v>39036</v>
       </c>
       <c r="G21" s="15">
-        <v>290.36</v>
+        <v>363.03</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0228025699662</v>
+        <v>0.0252103734524</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1593,13 +1590,13 @@
         <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>66682</v>
+        <v>23525</v>
       </c>
       <c r="G22" s="15">
-        <v>241.76</v>
+        <v>342.78</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0189859116787</v>
+        <v>0.0238041258629</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1622,13 +1619,13 @@
         <v>17</v>
       </c>
       <c r="F23" s="14">
-        <v>771</v>
+        <v>21712</v>
       </c>
       <c r="G23" s="15">
-        <v>201.80</v>
+        <v>309.35</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0158477704201</v>
+        <v>0.0214826020645</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1648,16 +1645,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F24" s="14">
-        <v>26786</v>
+        <v>815</v>
       </c>
       <c r="G24" s="15">
-        <v>200</v>
+        <v>248.21</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0157064127057</v>
+        <v>0.0172367760092</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1677,16 +1674,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F25" s="14">
-        <v>5542</v>
+        <v>70410</v>
       </c>
       <c r="G25" s="15">
-        <v>158.12</v>
+        <v>236.47</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0124174898851</v>
+        <v>0.0164214996289</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1706,16 +1703,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F26" s="14">
-        <v>21462</v>
+        <v>29561</v>
       </c>
       <c r="G26" s="15">
-        <v>119.40</v>
+        <v>191.13</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0093767283853</v>
+        <v>0.0132728939149</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1735,16 +1732,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>3851</v>
+        <v>22653</v>
       </c>
       <c r="G27" s="15">
-        <v>69.20</v>
+        <v>120.19</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0054344187961</v>
+        <v>0.0083465134706</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2259,10 +2256,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="9">
-        <v>2.38</v>
+        <v>71.53</v>
       </c>
       <c r="H55" s="10">
-        <v>0.0001869063111</v>
+        <v>0.0049673525963</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>13</v>
@@ -2296,10 +2293,10 @@
         <v>13</v>
       </c>
       <c r="G57" s="18">
-        <v>1.3324098000011873</v>
+        <v>-71.2853163000018</v>
       </c>
       <c r="H57" s="19">
-        <v>0.00010463689106008152</v>
+        <v>-0.004950360701859955</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>13</v>
@@ -2325,10 +2322,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="18">
-        <v>12733.6524098</v>
+        <v>14400.0246837</v>
       </c>
       <c r="H58" s="19">
-        <v>0.9999999999989598</v>
+        <v>0.9999999999992404</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>13</v>
@@ -2401,11 +2398,6 @@
     <row r="83" ht="15">
       <c r="B83" s="21" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="84" ht="15">
-      <c r="B84" s="21" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
